--- a/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente</t>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,41; 100,0</t>
+          <t>21,34; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,76; 100,0</t>
+          <t>68,08; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,79; 96,35</t>
+          <t>60,61; 96,38</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,73; 96,45</t>
+          <t>78,8; 96,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,61; 100,0</t>
+          <t>81,19; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,34; 96,83</t>
+          <t>85,82; 96,86</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,36; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,72; 95,55</t>
+          <t>78,94; 95,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,56; 99,12</t>
+          <t>87,44; 99,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,33; 96,29</t>
+          <t>86,76; 96,7</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9077</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>943; 4421</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4279; 6285</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6488; 10318</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>29570</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28498</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>58067</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>25819; 31660</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>24270; 29891</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53771; 60688</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4693</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12993</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>37450</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42688</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80137</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>33060; 40102</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38889; 44090</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74918; 83506</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 100,0</t>
+          <t>21,69; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,08; 100,0</t>
+          <t>69,99; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,61; 96,38</t>
+          <t>58,26; 96,42</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,8; 96,63</t>
+          <t>78,46; 96,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,19; 100,0</t>
+          <t>83,1; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,82; 96,86</t>
+          <t>85,37; 96,84</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,94; 95,76</t>
+          <t>79,97; 95,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,44; 99,13</t>
+          <t>86,39; 99,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,76; 96,7</t>
+          <t>87,28; 96,68</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>943; 4421</t>
+          <t>959; 4421</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4279; 6285</t>
+          <t>4399; 6285</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6488; 10318</t>
+          <t>6238; 10323</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25819; 31660</t>
+          <t>25707; 31575</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24270; 29891</t>
+          <t>24838; 29891</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53771; 60688</t>
+          <t>53486; 60674</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33060; 40102</t>
+          <t>33489; 40057</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38889; 44090</t>
+          <t>38422; 44091</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74918; 83506</t>
+          <t>75373; 83490</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 100,0</t>
+          <t>67,37; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,99; 100,0</t>
+          <t>16,82; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,26; 96,42</t>
+          <t>60,29; 97,1</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,46; 96,37</t>
+          <t>82,79; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,1; 100,0</t>
+          <t>78,22; 96,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,37; 96,84</t>
+          <t>85,26; 96,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,97; 95,65</t>
+          <t>86,01; 99,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,39; 99,13</t>
+          <t>79,35; 95,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,28; 96,68</t>
+          <t>86,83; 96,34</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9092</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>959; 4421</t>
+          <t>4023; 5971</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4399; 6285</t>
+          <t>780; 4638</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6238; 10323</t>
+          <t>6396; 10301</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58067</t>
+          <t>54175</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25707; 31575</t>
+          <t>23324; 28173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24838; 29891</t>
+          <t>23776; 29245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53486; 60674</t>
+          <t>49937; 56610</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12476</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>75743</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33489; 40057</t>
+          <t>36010; 41558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38422; 44091</t>
+          <t>31567; 37926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75373; 83490</t>
+          <t>70902; 78667</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>73,72%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>67,37; 100,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16,82; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60,29; 97,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>89,83%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>82,79; 100,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>78,22; 96,22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>85,26; 96,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>89,17%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>86,01; 99,26</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>79,35; 95,33</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86,83; 96,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9500299724624338</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7372294287165594</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.857005040903465</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5673</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3419</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9092</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.6737037921986464</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1682337069681491</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.602921153292403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4023; 5971</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>780; 4638</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6396; 10301</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.970966472811671</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9537927573682586</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8982930633509629</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9249903484821712</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>26871</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>27304</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54175</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8279016752033004</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.7822488755944834</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8526308798980046</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>23324; 28173</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23776; 29245</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>49937; 56610</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9621760039282321</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.966564667480849</v>
       </c>
     </row>
     <row r="10">
@@ -974,70 +662,40 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7725</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4751</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12476</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1047,69 +705,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9617813393191524</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8916626294165131</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9276177273610036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>40269</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>35473</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75743</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8600731094049333</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7934873386867402</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8683373196577306</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>36010; 41558</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>31567; 37926</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70902; 78667</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9925680317576339</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9533162452234279</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9634319325998786</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +769,364 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5673</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3419</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9092</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4023</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>780</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6396</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>5971</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4638</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>26871</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>27304</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>54175</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>23324</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>23776</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>49937</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>28173</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29245</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>56610</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>7725</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>4751</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>12476</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>40269</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>35473</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>75743</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>36010</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>31567</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>70902</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>41558</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>37926</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>78667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>